--- a/data/credit_bond_all_2026-09-23.xlsx
+++ b/data/credit_bond_all_2026-09-23.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-25" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
     </row>

--- a/data/credit_bond_all_2026-09-23.xlsx
+++ b/data/credit_bond_all_2026-09-23.xlsx
@@ -8834,74 +8834,70 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>电投KY22</t>
+          <t>26重庆三峡银行债01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-23 19:00</t>
+          <t>09-23 17:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>246152.SH</t>
+          <t>212680061.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>1.10 ~ 2.10</t>
-        </is>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="G38" s="3"/>
       <c r="H38" s="4" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>32.06</v>
+        <v>37.06</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25中电投MTN001B</t>
+          <t>25三峡银行科创债01(柜台)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>3.40Y+N</t>
+          <t>4.00Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.7291</t>
+          <t>1.7065</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.7400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>国家电力投资集团有限公司</t>
+          <t>重庆三峡银行股份有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 47.11</t>
+          <t>A- 66.24</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8911,7 +8907,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-23 15:00</t>
+          <t>09-23 09:30</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8924,60 +8920,50 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="U38" s="4" t="n">
-        <v>3.1625</v>
-      </c>
+      <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X38" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z38" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="AA38" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括偿还有息债务、补充流动资金等符合法律法规要求的用途。</t>
-        </is>
-      </c>
-      <c r="AC38" s="3" t="inlineStr">
-        <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,东方证券股份有限公司,光大证券股份有限公司,平安证券股份有限公司,国开证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>国家电力投资集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第四期)</t>
+          <t>重庆三峡银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8993,12 +8979,12 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AN38" s="3" t="inlineStr">
@@ -9008,32 +8994,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9048,12 +9034,12 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY38" s="3" t="inlineStr">
@@ -9066,22 +9052,22 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行债01</t>
+          <t>26冀中能源MTN020A</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-23 17:00</t>
+          <t>09-23 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>212680061.IB</t>
+          <t>102683821.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -9090,46 +9076,50 @@
       <c r="F39" s="4" t="n">
         <v>2.0</v>
       </c>
-      <c r="G39" s="3"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
       <c r="H39" s="4" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>37.06</v>
+        <v>65.18</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>25三峡银行科创债01(柜台)</t>
+          <t>26冀中能源MTN019A</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>4.00Y</t>
+          <t>1.99Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.7065</t>
+          <t>1.9500</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9299/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司</t>
+          <t>冀中能源集团有限责任公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>A- 66.24</t>
+          <t>C 26.17</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9139,12 +9129,12 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-23 09:30</t>
+          <t>09-23 10:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -9152,16 +9142,18 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>2.65</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9170,17 +9162,25 @@
         </is>
       </c>
       <c r="Z39" s="3"/>
-      <c r="AA39" s="3"/>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>河北省-邢台市</t>
+        </is>
+      </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC39" s="3"/>
+          <t>本期债务融资工具基础发行金额0亿元,发行金额上限为人民币5亿元。募集资金拟用于偿还发行人的有息债务。</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>天津银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司2026年金融债券(第一期)</t>
+          <t>冀中能源集团有限责任公司2026年度第二十期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9205,10 +9205,14 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2029-09-24</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2028-09-24</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -9216,7 +9220,7 @@
       </c>
       <c r="AM39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN39" s="3" t="inlineStr">
@@ -9226,32 +9230,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9279,79 +9283,81 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="AZ39" s="3"/>
+      <c r="AZ39" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26冀中能源MTN020A</t>
+          <t>26盐镇02</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>09-23 18:00</t>
+          <t>09-23 19:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>102683821.IB</t>
+          <t>284130.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>65.18</v>
+        <v>60.27</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26冀中能源MTN019A</t>
+          <t>26盐镇01</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>1.99Y</t>
+          <t>4.58Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.9500</t>
+          <t>1.9980</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.9299/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>冀中能源集团有限责任公司</t>
+          <t>盐城市城镇化建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C 26.17</t>
+          <t>C- 13.21</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9361,12 +9367,12 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-23 10:00</t>
+          <t>09-23 15:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -9375,7 +9381,7 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
@@ -9385,34 +9391,34 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>河北省-邢台市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具基础发行金额0亿元,发行金额上限为人民币5亿元。募集资金拟用于偿还发行人的有息债务。</t>
+          <t>本期债券募集资金不超过5.00亿元(含5.00亿元),拟全部用于置换偿还子公司盐城市盐都交通建设发展有限公司公司债券本金的自有资金。[23盐交03]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>天津银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中邮证券有限责任公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9422,32 +9428,28 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>冀中能源集团有限责任公司2026年度第二十期中期票据(品种一)</t>
+          <t>盐城市城镇化建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2028-09-24</t>
-        </is>
-      </c>
-      <c r="AK40" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-24</t>
+        </is>
+      </c>
+      <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9462,7 +9464,7 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
@@ -9472,22 +9474,22 @@
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9515,14 +9517,12 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="AZ40" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ40" s="3"/>
     </row>
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26盐镇02</t>
+          <t>26抚州03</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>284130.SH</t>
+          <t>246118.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -9541,55 +9541,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>60.27</v>
+        <v>54.27</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26盐镇01</t>
+          <t>26抚州投资MTN001</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>4.58Y</t>
+          <t>4.87Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.9980</t>
+          <t>1.8289</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8150</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>盐城市城镇化建设投资集团有限公司</t>
+          <t>抚州市市属国有资产投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 13.21</t>
+          <t>C+ 32.74</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9613,17 +9613,17 @@
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9634,17 +9634,17 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>江西省-抚州市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过5.00亿元(含5.00亿元),拟全部用于置换偿还子公司盐城市盐都交通建设发展有限公司公司债券本金的自有资金。[23盐交03]</t>
+          <t>本期债券为本次债券项下第一期发行发行规模为不超过1.00亿元(含1.00亿元)本期公司债券募集资金扣除发行费用后拟全部用于置换本期债券发行前3个月内偿还到期公司债券本金已使用的自有资金[21抚州04]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中邮证券有限责任公司</t>
+          <t>光大证券股份有限公司,国投证券股份有限公司,财信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9665,12 +9665,12 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>盐城市城镇化建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>抚州市市属国有资产投资控股集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN41" s="3" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
@@ -9706,17 +9706,17 @@
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
@@ -9754,7 +9754,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26抚州03</t>
+          <t>26汕尾交投01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>246118.SH</t>
+          <t>520488.SZ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -9773,55 +9773,47 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1.0</v>
+        <v>2.8</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1.0</v>
+        <v>2.4</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>54.27</v>
+        <v>53.27</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>26抚州投资MTN001</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>4.87Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.8289</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/1.8150</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>抚州市市属国有资产投资控股集团有限公司</t>
+          <t>汕尾市交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.74</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9845,19 +9837,15 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>2.7</v>
+        <v>3.67</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t>1.79%~1.89%</t>
-        </is>
-      </c>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X42" s="3"/>
       <c r="Y42" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9866,20 +9854,24 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>江西省-抚州市</t>
+          <t>广东省-汕尾市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券为本次债券项下第一期发行发行规模为不超过1.00亿元(含1.00亿元)本期公司债券募集资金扣除发行费用后拟全部用于置换本期债券发行前3个月内偿还到期公司债券本金已使用的自有资金[21抚州04]</t>
+          <t>本期债券募集资金扣除发行费用及担保费用后,拟将2.00亿元募集资金用于白沙湖项目建设和运营,2.80亿元偿还有息债务,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,国投证券股份有限公司,财信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD42" s="3"/>
+          <t>粤开证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr">
+        <is>
+          <t>广东粤财融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE42" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -9892,17 +9884,17 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>抚州市市属国有资产投资控股集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>汕尾市交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
@@ -9913,12 +9905,12 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t/>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN42" s="3" t="inlineStr">
@@ -9928,14 +9920,10 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP42" s="3"/>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -9963,7 +9951,7 @@
       </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW42" s="3" t="inlineStr">
@@ -9986,7 +9974,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26汕尾交投01</t>
+          <t>26汕尾交投02</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9996,7 +9984,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>520488.SZ</t>
+          <t>520503.SZ</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -10005,7 +9993,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2.8</v>
+        <v>2.0</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>2.4</v>
@@ -10016,10 +10004,10 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>53.27</v>
+        <v>52.27</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -10069,7 +10057,7 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>3.67</v>
+        <v>3.21</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
@@ -10077,7 +10065,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X43" s="3"/>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.92%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -10101,7 +10093,7 @@
       </c>
       <c r="AD43" s="3" t="inlineStr">
         <is>
-          <t>广东粤财融资担保集团有限公司</t>
+          <t>中证信用融资担保有限公司</t>
         </is>
       </c>
       <c r="AE43" s="3" t="inlineStr">
@@ -10121,7 +10113,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>汕尾市交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>汕尾市交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -10206,7 +10198,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26汕尾交投02</t>
+          <t>26泰凤01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10216,90 +10208,98 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>520503.SZ</t>
+          <t>284112.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2.4</v>
+        <v>5.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>52.27</v>
+        <v>41.06</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>26凤城河PPN003</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>2.91Y</t>
+        </is>
+      </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
+          <t>1.7279</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>1.7500/--</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>泰州凤城河建设发展有限公司</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>C- 19.69</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>09-23 16:00</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>汕尾市交通投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t>09-23 15:00</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10310,24 +10310,20 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>广东省-汕尾市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用及担保费用后,拟将2.00亿元募集资金用于白沙湖项目建设和运营,2.80亿元偿还有息债务,且不用于新股配售、申购,或用于股票及其衍生品种、可转换公司债券等的交易及其他非生产性支出</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟用于偿还公司到期的公司债券本金。[23泰凤01]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>粤开证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD44" s="3" t="inlineStr">
-        <is>
-          <t>中证信用融资担保有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10340,12 +10336,12 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>汕尾市交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>泰州凤城河建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10355,7 +10351,7 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-09-24</t>
+          <t>2029-09-24</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
@@ -10366,7 +10362,7 @@
       </c>
       <c r="AM44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN44" s="3" t="inlineStr">
@@ -10379,20 +10375,24 @@
           <t>类城投</t>
         </is>
       </c>
-      <c r="AP44" s="3"/>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="AV44" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW44" s="3" t="inlineStr">
@@ -10430,7 +10430,7 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26泰凤01</t>
+          <t>26锡铁投03</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10440,30 +10440,30 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>284112.SH</t>
+          <t>520504.SZ</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>5.0</v>
+        <v>5.84</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>5.0</v>
+        <v>5.84</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>41.06</v>
+        <v>21.93</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -10472,32 +10472,32 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26凤城河PPN003</t>
+          <t>26锡铁投01</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>4.36Y+5.00Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.7279</t>
+          <t>1.7699</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司</t>
+          <t>无锡地铁投资发展有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C- 19.69</t>
+          <t>B- 42.28</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-23 16:00</t>
+          <t>09-23 15:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10521,7 +10521,7 @@
         </is>
       </c>
       <c r="U45" s="4" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
@@ -10531,28 +10531,28 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟用于偿还公司到期的公司债券本金。[23泰凤01]</t>
+          <t>本期债券的募集资金扣除发行费用后,拟将5.84亿元用于偿还公司有息债务</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>天风证券股份有限公司,方正证券承销保荐有限责任公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
@@ -10568,12 +10568,12 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>泰州凤城河建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>无锡地铁投资发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2029-09-24</t>
+          <t>2036-09-24</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10604,37 +10604,33 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP45" s="3"/>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-24</t>
         </is>
       </c>
       <c r="AV45" s="3" t="inlineStr">
@@ -10644,7 +10640,7 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
@@ -10662,7 +10658,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26锡铁投03</t>
+          <t>26宜经02</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10672,103 +10668,103 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>520504.SZ</t>
+          <t>284066.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>5.84</v>
+        <v>4.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>5.84</v>
+        <v>4.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>21.93</v>
+        <v>39.27</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>25宜经01</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>3.51Y</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1.8223</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>宜兴经开区投资发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>C- 13.31</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>09-23 15:00</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>26锡铁投01</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>4.36Y+5.00Y</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>1.7699</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>无锡地铁投资发展有限公司</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>B- 42.28</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>09-23 15:00</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
@@ -10779,12 +10775,12 @@
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后,拟将5.84亿元用于偿还公司有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[22宜经02]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,方正证券承销保荐有限责任公司,东吴证券股份有限公司</t>
+          <t>东吴证券股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
@@ -10800,12 +10796,12 @@
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>无锡地铁投资发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>宜兴经开区投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10815,56 +10811,60 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2036-09-24</t>
+          <t>2031-09-24</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AO46" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP46" s="3"/>
-      <c r="AQ46" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR46" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AS46" s="3" t="inlineStr">
-        <is>
-          <t>其他非银</t>
-        </is>
-      </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-24</t>
-        </is>
-      </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -10890,7 +10890,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26弥工债</t>
+          <t>26上饶产投MTN001</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>284053.SH</t>
+          <t>102683800.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10909,55 +10909,55 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>3.00 ~ 4.50</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>3.47</v>
+        <v>2.05</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>206.27</v>
+        <v>64.27</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>23弥工01</t>
+          <t>26饶产01</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>79D</t>
+          <t>2.35Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>2.0666</t>
+          <t>1.9339</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>--/2.0000</t>
+          <t>1.9100/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>弥勒工业园区投资开发有限公司</t>
+          <t>上饶市产业投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C 27.50</t>
+          <t>B- 40.00</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10967,12 +10967,12 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>09-23 15:00</t>
+          <t>09-23 09:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
@@ -10981,44 +10981,46 @@
         </is>
       </c>
       <c r="U47" s="4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="V47" s="3"/>
+        <v>2.47</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>3.00%~3.10%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>云南省-红河哈尼族彝族自治州</t>
+          <t>江西省-上饶市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,将全部用于偿还到期的“23弥工01”公司债券本金。[23弥工01]</t>
+          <t>本次债务融资工具发行金额为10亿元,募集资金拟全部用于偿还发行人到期有息债务</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>红塔证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
@@ -11028,17 +11030,17 @@
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>弥勒工业园区投资开发有限公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>上饶市产业投资发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
@@ -11049,132 +11051,134 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM47" s="3" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr">
+        <is>
+          <t>金属和非金属矿产</t>
+        </is>
+      </c>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>常用有色金属</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>工业金属</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY47" s="3" t="inlineStr">
+        <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AO47" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>9*无效</t>
-        </is>
-      </c>
-      <c r="AQ47" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR47" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV47" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW47" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX47" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AZ47" s="3"/>
+      <c r="AZ47" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26宜经02</t>
+          <t>26九江国投MTN002</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>09-23 19:00</t>
+          <t>09-23 18:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>284066.SH</t>
+          <t>102683818.IB</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>4.0</v>
+        <v>10.6</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4.0</v>
+        <v>10.6</v>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>39.27</v>
+        <v>38.06</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>25宜经01</t>
+          <t>22九江国控债01(柜台)</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>3.51Y</t>
+          <t>3.06Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.8223</t>
+          <t>1.6503</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -11184,12 +11188,12 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>宜兴经开区投资发展集团有限公司</t>
+          <t>九江市国有投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C- 13.31</t>
+          <t>B- 46.76</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11199,12 +11203,12 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-23 15:00</t>
+          <t>09-23 09:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
@@ -11213,44 +11217,46 @@
         </is>
       </c>
       <c r="U48" s="4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V48" s="3"/>
+        <v>4.9151</v>
+      </c>
+      <c r="V48" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江西省-九江市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,将全部用于偿还到期公司债券本金[22宜经02]</t>
+          <t>本期中期票据发行规模10.6亿元,募集资金拟全部用于偿还有息债务[23九江国投PPN001]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天风证券股份有限公司</t>
+          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
@@ -11260,33 +11266,33 @@
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>宜兴经开区投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>九江市国有投资控股集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2031-09-24</t>
+          <t>2029-09-24</t>
         </is>
       </c>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN48" s="3" t="inlineStr">
@@ -11304,24 +11310,12 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="AQ48" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR48" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
+      <c r="AQ48" s="3"/>
+      <c r="AR48" s="3"/>
+      <c r="AS48" s="3"/>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
@@ -11354,74 +11348,74 @@
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26上饶产投MTN001</t>
+          <t>26石狮农商行小微债01</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>09-23 18:00</t>
+          <t>09-23 12:00</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>102683800.IB</t>
+          <t>212680059.IB</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
+          <t>1.45 ~ 1.95</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>64.27</v>
+        <v>41.06</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26饶产01</t>
+          <t>25石狮农商小微债01(柜台)</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2.35Y</t>
+          <t>2.10Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1.9339</t>
+          <t>1.7328</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>1.9100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>上饶市产业投资发展集团有限公司</t>
+          <t>福建石狮农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>B- 40.00</t>
+          <t>D 3.33</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11436,20 +11430,16 @@
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="U49" s="4" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V49" s="4" t="n">
-        <v>1.5</v>
-      </c>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -11457,39 +11447,43 @@
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z49" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>江西省-上饶市</t>
+          <t>福建省-泉州市</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>本次债务融资工具发行金额为10亿元,募集资金拟全部用于偿还发行人到期有息债务</t>
+          <t>本次小型微型企业贷款专项金融债券的募集资金将依据适用法律和监管部门的批准,专项用于发放小微企业贷款</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF49" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG49" s="3" t="inlineStr">
@@ -11499,7 +11493,7 @@
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>上饶市产业投资发展集团有限公司2026年度第一期中期票据</t>
+          <t>福建石狮农村商业银行股份有限公司2026年第一期小型微型企业贷款专项金融债券</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11509,53 +11503,53 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2031-09-24</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AM49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>常用有色金属</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
@@ -11583,66 +11577,64 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="AZ49" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ49" s="3"/>
     </row>
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26九江国投MTN002</t>
+          <t>26港控01</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>09-23 18:00</t>
+          <t>09-23 19:00</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>102683818.IB</t>
+          <t>283962.SH</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>10.6</v>
+        <v>5.0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>10.6</v>
+        <v>5.0</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>38.06</v>
+        <v>49.27</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>22九江国控债01(柜台)</t>
+          <t>25港控04</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>3.06Y</t>
+          <t>3.89Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.6503</t>
+          <t>1.8086</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -11652,12 +11644,12 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>九江市国有投资控股集团有限公司</t>
+          <t>珠海港控股集团有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>B- 46.76</t>
+          <t>C- 21.46</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11667,33 +11659,31 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>09-23 09:00</t>
+          <t>09-23 16:00</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>4.9151</v>
-      </c>
-      <c r="V50" s="4" t="n">
-        <v>20.0</v>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
@@ -11704,23 +11694,23 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>江西省-九江市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10.6亿元,募集资金拟全部用于偿还有息债务[23九江国投PPN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟全部用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
       <c r="AE50" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF50" s="3" t="inlineStr">
@@ -11730,56 +11720,72 @@
       </c>
       <c r="AG50" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>九江市国有投资控股集团有限公司2026年度第二期中期票据</t>
+          <t>珠海港控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2029-09-24</t>
-        </is>
-      </c>
-      <c r="AK50" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK50" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL50" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AM50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ50" s="3"/>
-      <c r="AR50" s="3"/>
-      <c r="AS50" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11812,74 +11818,74 @@
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26石狮农商行小微债01</t>
+          <t>26中证15</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>09-23 12:00</t>
+          <t>09-23 19:00</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>212680059.IB</t>
+          <t>245719.SH</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+3+3+3+3</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.45 ~ 1.95</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>41.06</v>
+        <v>-33.16</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>25石狮农商小微债01(柜台)</t>
+          <t>26中证K3</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2.10Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.7328</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6000/1.5900</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>福建石狮农村商业银行股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>D 3.33</t>
+          <t>A- 61.39</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11889,7 +11895,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>09-23 09:00</t>
+          <t>09-23 15:00</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -11902,62 +11908,64 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U51" s="3"/>
+      <c r="U51" s="4" t="n">
+        <v>2.45</v>
+      </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.58%~1.68%</t>
         </is>
       </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本次小型微型企业贷款专项金融债券的募集资金将依据适用法律和监管部门的批准,专项用于发放小微企业贷款</t>
+          <t>本期募集资金扣除发行等相关费用后不用于弥补亏损和非生产性支出,全部用于偿还公司债券[21中证Y2,26中证S1,23中证14,21中证10]</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>广发证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG51" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>福建石狮农村商业银行股份有限公司2026年第一期小型微型企业贷款专项金融债券</t>
+          <t>中信证券股份有限公司2026年面向专业机构投资者公开发行公司债券(第九期)</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
@@ -11967,60 +11975,64 @@
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
+          <t>2041-09-28</t>
+        </is>
+      </c>
+      <c r="AK51" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
           <t>2029-09-28</t>
         </is>
       </c>
-      <c r="AK51" s="3"/>
-      <c r="AL51" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AM51" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO51" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ51" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR51" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS51" s="3" t="inlineStr">
-        <is>
-          <t>农商行</t>
-        </is>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV51" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -12028,7 +12040,7 @@
       </c>
       <c r="AW51" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX51" s="3" t="inlineStr">
@@ -12046,59 +12058,59 @@
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26港控01</t>
+          <t>26成都先导MTN001(科创债)</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>09-23 19:00</t>
+          <t>09-23 18:00</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>283962.SH</t>
+          <t>102690057.IB</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1.5Y</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>49.27</v>
+        <v>152.08</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>25港控04</t>
+          <t>25安东石油MTN001(科创债)</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>3.89Y</t>
+          <t>2.08Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.8086</t>
+          <t>1.9737</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -12108,12 +12120,12 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>珠海港控股集团有限公司</t>
+          <t>成都先导药物开发股份有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C- 21.46</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12123,7 +12135,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>09-23 16:00</t>
+          <t>09-23 09:00</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -12133,93 +12145,91 @@
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="U52" s="4" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="V52" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>2.4</v>
+      </c>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟全部用于偿还有息债务。</t>
+          <t>发行人本次发行金额2亿元,其中1.25亿元用于并购,0.27亿元用于发行人研发投入,0.48亿元用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,申万宏源证券有限公司</t>
+          <t>成都银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG52" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>珠海港控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>成都先导药物开发股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ52" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK52" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-03-24</t>
+        </is>
+      </c>
+      <c r="AK52" s="3"/>
       <c r="AL52" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AN52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AO52" s="3" t="inlineStr">
@@ -12227,29 +12237,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP52" s="3"/>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>专业服务</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>行业支持</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>行业支持</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>医疗服务</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12282,7 +12288,7 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26中证15</t>
+          <t>26如东02</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -12292,64 +12298,64 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>245719.SH</t>
+          <t>284109.SH</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3+3+3+3+3</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>-33.16</v>
+        <v>51.27</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26中证K3</t>
+          <t>26如东01</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.8697</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>1.6000/1.5900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>如东县金鑫交通工程建设投资有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>A- 61.39</t>
+          <t>D+ 8.58</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12373,53 +12379,45 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X53" s="3" t="inlineStr">
-        <is>
-          <t>1.58%~1.68%</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X53" s="3"/>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z53" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期募集资金扣除发行等相关费用后不用于弥补亏损和非生产性支出,全部用于偿还公司债券[21中证Y2,26中证S1,23中证14,21中证10]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用10.00亿元偿还回售公司债券本金[23如东02]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,平安证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG53" s="3" t="inlineStr">
@@ -12429,22 +12427,22 @@
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司2026年面向专业机构投资者公开发行公司债券(第九期)</t>
+          <t>如东县金鑫交通工程建设投资有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2041-09-28</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK53" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL53" s="3" t="inlineStr">
@@ -12454,7 +12452,7 @@
       </c>
       <c r="AM53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN53" s="3" t="inlineStr">
@@ -12464,37 +12462,37 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV53" s="3" t="inlineStr">
@@ -12504,7 +12502,7 @@
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
@@ -12522,74 +12520,74 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26成都先导MTN001(科创债)</t>
+          <t>26大宁02</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>09-23 18:00</t>
+          <t>09-23 19:00</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>102690057.IB</t>
+          <t>284019.SH</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>1.5Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>2.78</v>
+        <v>1.8</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>152.08</v>
+        <v>29.54</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>25安东石油MTN001(科创债)</t>
+          <t>26大宁01</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2.08Y</t>
+          <t>4.52Y+2.00Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.9737</t>
+          <t>1.8093</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8500/1.7600</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>成都先导药物开发股份有限公司</t>
+          <t>上海大宁资产经营(集团)有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 25.69</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12599,7 +12597,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>09-23 09:00</t>
+          <t>09-23 15:00</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -12609,122 +12607,124 @@
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="V54" s="4" t="n">
-        <v>2.4</v>
-      </c>
+        <v>4.64</v>
+      </c>
+      <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>上海市-静安区</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行金额2亿元,其中1.25亿元用于并购,0.27亿元用于发行人研发投入,0.48亿元用于偿还发行人有息债务。</t>
+          <t>本期债券的募集资金总额不超过(含)5.00亿元,扣除发行费用后,拟全部用于偿还回售公司债券本金。[21大宁02]</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>成都银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>中泰证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
       <c r="AE54" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF54" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG54" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>成都先导药物开发股份有限公司2026年度第一期科技创新债券</t>
+          <t>上海大宁资产经营(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2028-03-24</t>
+          <t>2033-09-28</t>
         </is>
       </c>
       <c r="AK54" s="3"/>
       <c r="AL54" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AM54" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP54" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>专业服务</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>行业支持</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>行业支持</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>医疗服务</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AV54" s="3" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX54" s="3" t="inlineStr">
@@ -12752,7 +12752,7 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26如东02</t>
+          <t>26成兴03</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12762,64 +12762,64 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>284109.SH</t>
+          <t>284087.SH</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>51.27</v>
+        <v>68.54</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26如东01</t>
+          <t>26成兴02</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>6.29Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.8697</t>
+          <t>2.2599</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.3000/2.1000</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>如东县金鑫交通工程建设投资有限公司</t>
+          <t>泰兴市成兴国有资产经营投资有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.58</t>
+          <t>D 3.52</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12843,37 +12843,45 @@
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>2.53</v>
+        <v>4.87</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X55" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>2.23%~2.33%</t>
+        </is>
+      </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用10.00亿元偿还回售公司债券本金[23如东02]</t>
+          <t>本期债券募集资金扣除发行费用后,仅用于偿还“23成兴02”回售的公司债券本金[23成兴02]</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD55" s="3"/>
+          <t>东吴证券股份有限公司,申港证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr">
+        <is>
+          <t>江苏省信用增进有限责任公司</t>
+        </is>
+      </c>
       <c r="AE55" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -12891,7 +12899,7 @@
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>如东县金鑫交通工程建设投资有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>泰兴市成兴国有资产经营投资有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12901,14 +12909,10 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK55" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2033-09-28</t>
+        </is>
+      </c>
+      <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
           <t/>
@@ -12916,7 +12920,7 @@
       </c>
       <c r="AM55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN55" s="3" t="inlineStr">
@@ -12926,12 +12930,12 @@
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
@@ -12941,12 +12945,12 @@
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
@@ -12961,7 +12965,7 @@
       </c>
       <c r="AV55" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW55" s="3" t="inlineStr">
@@ -12984,7 +12988,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26大宁02</t>
+          <t>电投KY22</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -12994,64 +12998,64 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>284019.SH</t>
+          <t>246152.SH</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>29.54</v>
+        <v>32.06</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26大宁01</t>
+          <t>25中电投MTN001B</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>4.52Y+2.00Y</t>
+          <t>3.40Y+N</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.8093</t>
+          <t>1.7291</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>1.8500/1.7600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>上海大宁资产经营(集团)有限公司</t>
+          <t>国家电力投资集团有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C 25.69</t>
+          <t>B- 47.11</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13071,42 +13075,42 @@
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="U56" s="4" t="n">
-        <v>4.64</v>
+        <v>3.1625</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X56" s="3" t="inlineStr">
-        <is>
-          <t>1.80%~1.90%</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X56" s="3"/>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z56" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>上海市-静安区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金总额不超过(含)5.00亿元,扣除发行费用后,拟全部用于偿还回售公司债券本金。[21大宁02]</t>
+          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括偿还有息债务、补充流动资金等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,东方证券股份有限公司,光大证券股份有限公司,平安证券股份有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
@@ -13117,7 +13121,7 @@
       </c>
       <c r="AF56" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG56" s="3" t="inlineStr">
@@ -13127,70 +13131,70 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>上海大宁资产经营(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>国家电力投资集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2033-09-28</t>
+          <t>2029-09-24</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM56" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO56" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ56" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR56" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS56" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT56" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU56" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
       <c r="AV56" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -13198,12 +13202,12 @@
       </c>
       <c r="AW56" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX56" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY56" s="3" t="inlineStr">
@@ -13216,74 +13220,74 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26成兴03</t>
+          <t>26南洋银行02</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>09-23 19:00</t>
+          <t>09-23 16:00</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>284087.SH</t>
+          <t>2626002.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>68.54</v>
+        <v>48.27</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26成兴02</t>
+          <t>24南洋银行08</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>6.29Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>2.2599</t>
+          <t>1.6398</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>2.3000/2.1000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>泰兴市成兴国有资产经营投资有限公司</t>
+          <t>南洋商业银行(中国)有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>D 3.52</t>
+          <t>D+ 7.60</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13293,7 +13297,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>09-23 15:00</t>
+          <t>09-23 09:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -13306,130 +13310,124 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U57" s="4" t="n">
-        <v>4.87</v>
-      </c>
+      <c r="U57" s="3"/>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X57" s="3" t="inlineStr">
-        <is>
-          <t>2.23%~2.33%</t>
-        </is>
-      </c>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X57" s="3"/>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z57" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,仅用于偿还“23成兴02”回售的公司债券本金[23成兴02]</t>
+          <t xml:space="preserve">本期债券募集资金将全部用于中国境内，主要用于支持符合国家政策导向的中长期优质资产业务，优化发行人资产负债结构，增加稳定的中长期资金来源，置换到期金融债券。 </t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,申港证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD57" s="3" t="inlineStr">
-        <is>
-          <t>江苏省信用增进有限责任公司</t>
-        </is>
-      </c>
+          <t>信达证券股份有限公司,华泰联合证券有限责任公司,中信证券股份有限公司,中国银行股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,兴业银行股份有限公司,中国银河证券股份有限公司,上海浦东发展银行股份有限公司,光大证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG57" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>泰兴市成兴国有资产经营投资有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>南洋商业银行(中国)有限公司2026年金融债券(第一期)(债券通)(品种二)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2033-09-28</t>
-        </is>
-      </c>
-      <c r="AK57" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK57" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL57" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP57" s="3"/>
+      <c r="AQ57" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>其他银行</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM57" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO57" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ57" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR57" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS57" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT57" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU57" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV57" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW57" s="3" t="inlineStr">
@@ -13452,7 +13450,7 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26南洋银行02</t>
+          <t>26青岛农商02</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13462,49 +13460,49 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>2626002.IB</t>
+          <t>2621007.IB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>6.0</v>
+        <v>25.0</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>48.27</v>
+        <v>30.06</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>24南洋银行08</t>
+          <t>26青岛农商行小微债01</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.6398</t>
+          <t>1.5975</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -13514,12 +13512,12 @@
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>南洋商业银行(中国)有限公司</t>
+          <t>青岛农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.60</t>
+          <t>B- 46.70</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13542,14 +13540,20 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U58" s="3"/>
+      <c r="U58" s="4" t="n">
+        <v>2.62</v>
+      </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X58" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>1.56%~1.66%</t>
+        </is>
+      </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13562,17 +13566,13 @@
       </c>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">本期债券募集资金将全部用于中国境内，主要用于支持符合国家政策导向的中长期优质资产业务，优化发行人资产负债结构，增加稳定的中长期资金来源，置换到期金融债券。 </t>
-        </is>
-      </c>
+          <t>山东省-青岛市</t>
+        </is>
+      </c>
+      <c r="AB58" s="3"/>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>信达证券股份有限公司,华泰联合证券有限责任公司,中信证券股份有限公司,中国银行股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,兴业银行股份有限公司,中国银河证券股份有限公司,上海浦东发展银行股份有限公司,光大证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,首创证券股份有限公司,光大证券股份有限公司,兴业银行股份有限公司,恒丰银行股份有限公司,渤海银行股份有限公司,中国邮政储蓄银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="AF58" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG58" s="3" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>南洋商业银行(中国)有限公司2026年金融债券(第一期)(债券通)(品种二)</t>
+          <t>青岛农村商业银行股份有限公司2026年第二期金融债券</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13603,14 +13603,10 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK58" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK58" s="3"/>
       <c r="AL58" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -13618,7 +13614,7 @@
       </c>
       <c r="AM58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN58" s="3" t="inlineStr">
@@ -13631,7 +13627,11 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP58" s="3"/>
+      <c r="AP58" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -13644,7 +13644,7 @@
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>其他银行</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
@@ -18532,74 +18532,74 @@
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26青岛农商02</t>
+          <t>26鲁高速SCP003</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>09-23 16:00</t>
+          <t>09-23 18:00</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>2621007.IB</t>
+          <t>012682347.IB</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.41Y</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="F80" s="4" t="n">
         <v>25.0</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.30 ~ 1.49</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>30.06</v>
+        <v>17.46</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>26青岛农商行小微债01</t>
+          <t>26鲁高速SCP002</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>84D</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>1.5975</t>
+          <t>1.4822</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>1.6050/1.5900</t>
+          <t>1.4800/1.3197</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>青岛农村商业银行股份有限公司</t>
+          <t>山东高速集团有限公司</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>B- 46.70</t>
+          <t>B- 42.01</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18614,26 +18614,28 @@
       </c>
       <c r="S80" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="T80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="U80" s="4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V80" s="3"/>
+        <v>1.028</v>
+      </c>
+      <c r="V80" s="4" t="n">
+        <v>1.01</v>
+      </c>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -18641,31 +18643,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z80" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z80" s="3"/>
       <c r="AA80" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
-        </is>
-      </c>
-      <c r="AB80" s="3"/>
+          <t>山东省</t>
+        </is>
+      </c>
+      <c r="AB80" s="3" t="inlineStr">
+        <is>
+          <t>本期超短期融资券基础发行金额20亿元，发行金额上限25亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
+        </is>
+      </c>
       <c r="AC80" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,首创证券股份有限公司,光大证券股份有限公司,兴业银行股份有限公司,恒丰银行股份有限公司,渤海银行股份有限公司,中国邮政储蓄银行股份有限公司,华夏银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,中国民生银行股份有限公司,恒丰银行股份有限公司</t>
         </is>
       </c>
       <c r="AD80" s="3"/>
       <c r="AE80" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF80" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG80" s="3" t="inlineStr">
@@ -18675,7 +18677,7 @@
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>青岛农村商业银行股份有限公司2026年第二期金融债券</t>
+          <t>山东高速集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
@@ -18685,13 +18687,17 @@
       </c>
       <c r="AJ80" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
-        </is>
-      </c>
-      <c r="AK80" s="3"/>
+          <t>2027-02-21</t>
+        </is>
+      </c>
+      <c r="AK80" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM80" s="3" t="inlineStr">
@@ -18701,37 +18707,37 @@
       </c>
       <c r="AN80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AO80" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP80" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ80" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR80" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS80" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT80" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU80" s="3" t="inlineStr">
@@ -18764,7 +18770,7 @@
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26鲁高速SCP003</t>
+          <t>26首旅SCP008</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -18774,64 +18780,64 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>012682347.IB</t>
+          <t>012682351.IB</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>0.41Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
         <v>20.0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.49</t>
+          <t>1.30 ~ 1.60</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>17.46</v>
+        <v>12.98</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>26鲁高速SCP002</t>
+          <t>24首旅MTN001</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>84D</t>
+          <t>110D</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>1.4822</t>
+          <t>1.5051</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>1.4800/1.3197</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司</t>
+          <t>北京首都旅游集团有限责任公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>B- 42.01</t>
+          <t>C 25.32</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18846,7 +18852,7 @@
       </c>
       <c r="S81" s="3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="T81" s="3" t="inlineStr">
@@ -18855,14 +18861,14 @@
         </is>
       </c>
       <c r="U81" s="4" t="n">
-        <v>1.028</v>
+        <v>2.54</v>
       </c>
       <c r="V81" s="4" t="n">
-        <v>1.01</v>
+        <v>1.0</v>
       </c>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
@@ -18878,17 +18884,17 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB81" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券基础发行金额20亿元，发行金额上限25亿元，募集资金用于偿还发行人本部及子公司有息负债及补充流动资金</t>
+          <t>发行人本期发行20亿元的超短期融资券，募集资金拟用于偿还首旅集团本部及下属子公司的有息负债</t>
         </is>
       </c>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,中国民生银行股份有限公司,恒丰银行股份有限公司</t>
+          <t>杭州银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
@@ -18909,7 +18915,7 @@
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>山东高速集团有限公司2026年度第三期超短期融资券</t>
+          <t>北京首都旅游集团有限责任公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -18919,14 +18925,10 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2027-02-21</t>
-        </is>
-      </c>
-      <c r="AK81" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-25</t>
+        </is>
+      </c>
+      <c r="AK81" s="3"/>
       <c r="AL81" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
@@ -18944,32 +18946,32 @@
       </c>
       <c r="AO81" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP81" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ81" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>消费者服务</t>
         </is>
       </c>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合消费者服务</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>综合消费者服务</t>
         </is>
       </c>
       <c r="AT81" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>旅游综合</t>
         </is>
       </c>
       <c r="AU81" s="3" t="inlineStr">
@@ -19002,7 +19004,7 @@
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26首旅SCP008</t>
+          <t>26成泰农商行二级资本债01</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -19012,49 +19014,49 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>012682351.IB</t>
+          <t>232680041.IB</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.60</t>
+          <t>2.30 ~ 2.80</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.32</v>
+        <v>2.44</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>12.98</v>
+        <v>75.93</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>24首旅MTN001</t>
+          <t>22金华成泰农商二级01(柜台)</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>110D</t>
+          <t>277D+5.00Y</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>1.5051</t>
+          <t>1.9953</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -19064,12 +19066,12 @@
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>北京首都旅游集团有限责任公司</t>
+          <t>浙江金华成泰农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>C 25.32</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19084,60 +19086,60 @@
       </c>
       <c r="S82" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="U82" s="4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>1.0</v>
-      </c>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>2.79%~2.89%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z82" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z82" s="3" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行20亿元的超短期融资券，募集资金拟用于偿还首旅集团本部及下属子公司的有息负债</t>
+          <t>本期债券募集资金将依据适用法律和监管部门的批准用于充实发行人二级资本</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AF82" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG82" s="3" t="inlineStr">
@@ -19147,7 +19149,7 @@
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>北京首都旅游集团有限责任公司2026年度第八期超短期融资券</t>
+          <t>浙江金华成泰农村商业银行股份有限公司2026年二级资本债券</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
@@ -19157,58 +19159,62 @@
       </c>
       <c r="AJ82" s="3" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
-        </is>
-      </c>
-      <c r="AK82" s="3"/>
+          <t>2036-09-28</t>
+        </is>
+      </c>
+      <c r="AK82" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL82" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM82" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AN82" s="3" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AM82" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="AN82" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
       <c r="AO82" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP82" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>消费者服务</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>综合消费者服务</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>综合消费者服务</t>
+          <t>农商行</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>旅游综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AV82" s="3" t="inlineStr">
@@ -19218,12 +19224,12 @@
       </c>
       <c r="AW82" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX82" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>二级资本工具</t>
         </is>
       </c>
       <c r="AY82" s="3" t="inlineStr">
@@ -19236,74 +19242,74 @@
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26成泰农商行二级资本债01</t>
+          <t>26桂铁08</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>09-23 18:00</t>
+          <t>09-23 19:00</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>232680041.IB</t>
+          <t>525026.SZ</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 2.80</t>
+          <t>1.30 ~ 2.00</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>2.44</v>
+        <v>1.53</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>75.93</v>
+        <v>26.18</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>22金华成泰农商二级01(柜台)</t>
+          <t>26桂铁06</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>277D+5.00Y</t>
+          <t>1.92Y</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.9953</t>
+          <t>1.6576</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/--</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>浙江金华成泰农村商业银行股份有限公司</t>
+          <t>广西铁路投资集团有限公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 43.11</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19313,7 +19319,7 @@
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>09-23 09:00</t>
+          <t>09-23 15:00</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr">
@@ -19326,62 +19332,60 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U83" s="3"/>
+      <c r="U83" s="4" t="n">
+        <v>5.3</v>
+      </c>
       <c r="V83" s="3"/>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>2.79%~2.89%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z83" s="3" t="inlineStr">
-        <is>
-          <t>AA-</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z83" s="3"/>
       <c r="AA83" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将依据适用法律和监管部门的批准用于充实发行人二级资本</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[21桂铁04]</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>东方证券股份有限公司,兴业证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD83" s="3"/>
       <c r="AE83" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF83" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG83" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>浙江金华成泰农村商业银行股份有限公司2026年二级资本债券</t>
+          <t>广西铁路投资集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
@@ -19391,22 +19395,18 @@
       </c>
       <c r="AJ83" s="3" t="inlineStr">
         <is>
-          <t>2036-09-28</t>
-        </is>
-      </c>
-      <c r="AK83" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-09-28</t>
+        </is>
+      </c>
+      <c r="AK83" s="3"/>
       <c r="AL83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM83" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN83" s="3" t="inlineStr">
@@ -19416,37 +19416,37 @@
       </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP83" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>农商行</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV83" s="3" t="inlineStr">
@@ -19456,12 +19456,12 @@
       </c>
       <c r="AW83" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX83" s="3" t="inlineStr">
         <is>
-          <t>二级资本工具</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY83" s="3" t="inlineStr">
@@ -19474,7 +19474,7 @@
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26桂铁08</t>
+          <t>26桂债04</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19484,64 +19484,64 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>525026.SZ</t>
+          <t>520498.SZ</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.00</t>
+          <t>1.90 ~ 2.50</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>26.18</v>
+        <v>69.06</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>26桂铁06</t>
+          <t>26桂债03</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>1.92Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>1.6576</t>
+          <t>2.1280</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>1.6800/--</t>
+          <t>2.1200/2.1000</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司</t>
+          <t>广西金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>B- 43.11</t>
+          <t>B- 44.11</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19565,17 +19565,17 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>5.3</v>
+        <v>3.76</v>
       </c>
       <c r="V84" s="3"/>
       <c r="W84" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>2.13%~2.23%</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
@@ -19591,12 +19591,12 @@
       </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[21桂铁04]</t>
+          <t>本期债券募集资金拟全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,兴业证券股份有限公司,平安证券股份有限公司</t>
+          <t>中国银河证券股份有限公司,华创证券有限责任公司,国海证券股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
@@ -19617,17 +19617,17 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>广西铁路投资集团有限公司2026年面向专业投资者公开发行公司债券(第四期)</t>
+          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ84" s="3" t="inlineStr">
         <is>
-          <t>2028-09-28</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK84" s="3"/>
@@ -19638,7 +19638,7 @@
       </c>
       <c r="AM84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AN84" s="3" t="inlineStr">
@@ -19648,32 +19648,32 @@
       </c>
       <c r="AO84" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP84" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ84" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT84" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU84" s="3" t="inlineStr">
@@ -19706,7 +19706,7 @@
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26桂债04</t>
+          <t>26揭投04</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -19716,64 +19716,64 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>520498.SZ</t>
+          <t>520505.SZ</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.50</t>
+          <t>1.50 ~ 2.80</t>
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>69.06</v>
+        <v>51.27</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>26桂债03</t>
+          <t>26揭投03</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.73Y</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>2.1280</t>
+          <t>1.9562</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>2.1200/2.1000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司</t>
+          <t>揭阳市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>B- 44.11</t>
+          <t>C- 24.38</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19797,41 +19797,45 @@
         </is>
       </c>
       <c r="U85" s="4" t="n">
-        <v>3.76</v>
+        <v>5.9</v>
       </c>
       <c r="V85" s="3"/>
       <c r="W85" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X85" s="3" t="inlineStr">
         <is>
-          <t>2.13%~2.23%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y85" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z85" s="3"/>
       <c r="AA85" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>广东省-揭阳市</t>
         </is>
       </c>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还有息债务</t>
+          <t>本期债券发行总额不超过人民币6亿元(含6亿元)。本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司,华创证券有限责任公司,国海证券股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD85" s="3"/>
+          <t>国信证券股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD85" s="3" t="inlineStr">
+        <is>
+          <t>中国投融资担保股份有限公司</t>
+        </is>
+      </c>
       <c r="AE85" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -19849,7 +19853,7 @@
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>揭阳市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(可持续挂钩)</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
@@ -19859,10 +19863,14 @@
       </c>
       <c r="AJ85" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
-        </is>
-      </c>
-      <c r="AK85" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK85" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL85" s="3" t="inlineStr">
         <is>
           <t/>
@@ -19870,7 +19878,7 @@
       </c>
       <c r="AM85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN85" s="3" t="inlineStr">
@@ -19880,27 +19888,27 @@
       </c>
       <c r="AO85" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP85" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ85" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR85" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS85" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT85" s="3" t="inlineStr">
@@ -19915,7 +19923,7 @@
       </c>
       <c r="AV85" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW85" s="3" t="inlineStr">
@@ -19938,7 +19946,7 @@
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>26揭投04</t>
+          <t>26国控02</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -19948,49 +19956,49 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>520505.SZ</t>
+          <t>284101.SH</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.80</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>51.27</v>
+        <v>38.27</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>26揭投03</t>
+          <t>24国控02</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>4.73Y</t>
+          <t>2.59Y</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>1.9562</t>
+          <t>1.7012</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -20000,12 +20008,12 @@
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>揭阳市投资控股集团有限公司</t>
+          <t>金华金开国有资本控股集团有限公司</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>C- 24.38</t>
+          <t>B- 38.50</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -20015,7 +20023,7 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>09-23 15:00</t>
+          <t>09-23 16:00</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr">
@@ -20029,45 +20037,41 @@
         </is>
       </c>
       <c r="U86" s="4" t="n">
-        <v>5.9</v>
+        <v>1.65</v>
       </c>
       <c r="V86" s="3"/>
       <c r="W86" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X86" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y86" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z86" s="3"/>
       <c r="AA86" s="3" t="inlineStr">
         <is>
-          <t>广东省-揭阳市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB86" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过人民币6亿元(含6亿元)。本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务。</t>
+          <t>本期公司债券发行总额不超过人民币13亿元(含13亿元),公司在扣除发行费用后,拟全部用于偿还回售的公司债券本金[23国控02]</t>
         </is>
       </c>
       <c r="AC86" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD86" s="3" t="inlineStr">
-        <is>
-          <t>中国投融资担保股份有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD86" s="3"/>
       <c r="AE86" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -20080,12 +20084,12 @@
       </c>
       <c r="AG86" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>揭阳市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)(可持续挂钩)</t>
+          <t>金华金开国有资本控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
@@ -20120,47 +20124,47 @@
       </c>
       <c r="AO86" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP86" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ86" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR86" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS86" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT86" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU86" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV86" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW86" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX86" s="3" t="inlineStr">
@@ -20178,7 +20182,7 @@
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>26国控02</t>
+          <t>26玉环02</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -20188,64 +20192,64 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>284101.SH</t>
+          <t>284137.SH</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>38.27</v>
+        <v>43.06</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>24国控02</t>
+          <t>26玉环01</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>2.59Y</t>
+          <t>2.51Y</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>1.7012</t>
+          <t>1.6423</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6600</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>金华金开国有资本控股集团有限公司</t>
+          <t>玉环市国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>B- 38.50</t>
+          <t>C- 12.31</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20255,7 +20259,7 @@
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>09-23 16:00</t>
+          <t>09-23 15:00</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr">
@@ -20269,38 +20273,34 @@
         </is>
       </c>
       <c r="U87" s="4" t="n">
-        <v>1.65</v>
+        <v>4.0417</v>
       </c>
       <c r="V87" s="3"/>
       <c r="W87" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X87" s="3" t="inlineStr">
-        <is>
-          <t>1.74%~1.84%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X87" s="3"/>
       <c r="Y87" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z87" s="3"/>
       <c r="AA87" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>浙江省-台州市</t>
         </is>
       </c>
       <c r="AB87" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行总额不超过人民币13亿元(含13亿元),公司在扣除发行费用后,拟全部用于偿还回售的公司债券本金[23国控02]</t>
+          <t>本期债券募集资金不超过12亿元(含12亿元),扣除发行费用后拟全部用于偿还到期公司债券的本金。[23玉投02]</t>
         </is>
       </c>
       <c r="AC87" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD87" s="3"/>
@@ -20321,7 +20321,7 @@
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>金华金开国有资本控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>玉环市国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
@@ -20331,14 +20331,10 @@
       </c>
       <c r="AJ87" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK87" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK87" s="3"/>
       <c r="AL87" s="3" t="inlineStr">
         <is>
           <t/>
@@ -20346,7 +20342,7 @@
       </c>
       <c r="AM87" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN87" s="3" t="inlineStr">
@@ -20366,17 +20362,17 @@
       </c>
       <c r="AQ87" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR87" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS87" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT87" s="3" t="inlineStr">
@@ -20386,7 +20382,7 @@
       </c>
       <c r="AU87" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV87" s="3" t="inlineStr">
@@ -20396,7 +20392,7 @@
       </c>
       <c r="AW87" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX87" s="3" t="inlineStr">
@@ -20414,7 +20410,7 @@
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>26玉环02</t>
+          <t>26金国04</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -20424,64 +20420,64 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>284137.SH</t>
+          <t>284039.SH</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>43.06</v>
+        <v>44.27</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>26玉环01</t>
+          <t>26金国03</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>2.51Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>1.6423</t>
+          <t>1.8572</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>--/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>玉环市国有资产投资经营集团有限公司</t>
+          <t>金华市国有资本运营有限公司</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>C- 12.31</t>
+          <t>C- 22.13</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20491,7 +20487,7 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>09-23 15:00</t>
+          <t>09-23 16:00</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr">
@@ -20505,34 +20501,38 @@
         </is>
       </c>
       <c r="U88" s="4" t="n">
-        <v>4.0417</v>
+        <v>4.0</v>
       </c>
       <c r="V88" s="3"/>
       <c r="W88" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X88" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X88" s="3" t="inlineStr">
+        <is>
+          <t>1.80%~1.90%</t>
+        </is>
+      </c>
       <c r="Y88" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z88" s="3"/>
       <c r="AA88" s="3" t="inlineStr">
         <is>
-          <t>浙江省-台州市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB88" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过12亿元(含12亿元),扣除发行费用后拟全部用于偿还到期公司债券的本金。[23玉投02]</t>
+          <t>本期债券的募集资金扣除发行费用后,仅全部用于偿还到期的公司债券本金[23金华05]</t>
         </is>
       </c>
       <c r="AC88" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD88" s="3"/>
@@ -20553,7 +20553,7 @@
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>玉环市国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>金华市国有资本运营有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
@@ -20563,10 +20563,14 @@
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
-        </is>
-      </c>
-      <c r="AK88" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK88" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL88" s="3" t="inlineStr">
         <is>
           <t/>
@@ -20589,7 +20593,7 @@
       </c>
       <c r="AP88" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ88" s="3" t="inlineStr">
@@ -20642,7 +20646,7 @@
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>26金国04</t>
+          <t>26义城01</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -20652,19 +20656,19 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>284039.SH</t>
+          <t>283933.SH</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -20672,44 +20676,44 @@
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>44.27</v>
+        <v>44.06</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>26金国03</t>
+          <t>24义城01</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>104D</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>1.8572</t>
+          <t>1.5490</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/1.5400</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>金华市国有资本运营有限公司</t>
+          <t>义乌市城市投资建设集团有限公司</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>C- 22.13</t>
+          <t>C- 19.90</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20733,17 +20737,17 @@
         </is>
       </c>
       <c r="U89" s="4" t="n">
-        <v>4.0</v>
+        <v>3.0923</v>
       </c>
       <c r="V89" s="3"/>
       <c r="W89" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X89" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y89" s="3" t="inlineStr">
@@ -20751,7 +20755,11 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z89" s="3"/>
+      <c r="Z89" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA89" s="3" t="inlineStr">
         <is>
           <t>浙江省-金华市</t>
@@ -20759,12 +20767,12 @@
       </c>
       <c r="AB89" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金扣除发行费用后,仅全部用于偿还到期的公司债券本金[23金华05]</t>
+          <t>本期债券发行总额为不超过人民币13亿元(含13亿元),募集资金扣除发行费用后,拟全部用于偿还到期的公司债券“23义城01”的本金[23义城01]</t>
         </is>
       </c>
       <c r="AC89" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD89" s="3"/>
@@ -20785,7 +20793,7 @@
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>金华市国有资本运营有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>义乌市城市投资建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
@@ -20795,14 +20803,10 @@
       </c>
       <c r="AJ89" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK89" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK89" s="3"/>
       <c r="AL89" s="3" t="inlineStr">
         <is>
           <t/>
@@ -20810,7 +20814,7 @@
       </c>
       <c r="AM89" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN89" s="3" t="inlineStr">
@@ -20825,22 +20829,22 @@
       </c>
       <c r="AP89" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ89" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR89" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS89" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT89" s="3" t="inlineStr">
@@ -20878,74 +20882,74 @@
     <row r="90" customHeight="true" ht="18.0">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>26义城01</t>
+          <t>26弥工债</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>09-23 19:00</t>
+          <t>09-23 18:00</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>283933.SH</t>
+          <t>284053.SH</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>13.0</v>
+        <v>9.0</v>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>3.00 ~ 4.50</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>1.73</v>
+        <v>3.47</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>44.06</v>
+        <v>206.27</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>24义城01</t>
+          <t>23弥工01</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>104D</t>
+          <t>79D</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>1.5490</t>
+          <t>2.0666</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>1.5800/1.5400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>义乌市城市投资建设集团有限公司</t>
+          <t>弥勒工业园区投资开发有限公司</t>
         </is>
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>C- 19.90</t>
+          <t>C 27.50</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -20955,7 +20959,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>09-23 16:00</t>
+          <t>09-23 15:00</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -20965,46 +20969,42 @@
       </c>
       <c r="T90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="U90" s="4" t="n">
-        <v>3.0923</v>
+        <v>2.01</v>
       </c>
       <c r="V90" s="3"/>
       <c r="W90" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X90" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>3.00%~3.10%</t>
         </is>
       </c>
       <c r="Y90" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z90" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z90" s="3"/>
       <c r="AA90" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>云南省-红河哈尼族彝族自治州</t>
         </is>
       </c>
       <c r="AB90" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额为不超过人民币13亿元(含13亿元),募集资金扣除发行费用后,拟全部用于偿还到期的公司债券“23义城01”的本金[23义城01]</t>
+          <t>本次公司债券募集资金扣除发行费用后,将全部用于偿还到期的“23弥工01”公司债券本金。[23弥工01]</t>
         </is>
       </c>
       <c r="AC90" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,国金证券股份有限公司</t>
+          <t>红塔证券股份有限公司</t>
         </is>
       </c>
       <c r="AD90" s="3"/>
@@ -21025,7 +21025,7 @@
       </c>
       <c r="AH90" s="3" t="inlineStr">
         <is>
-          <t>义乌市城市投资建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>弥勒工业园区投资开发有限公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI90" s="3" t="inlineStr">
@@ -21035,23 +21035,23 @@
       </c>
       <c r="AJ90" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2031-09-24</t>
         </is>
       </c>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AM90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AO90" s="3" t="inlineStr">
@@ -21061,7 +21061,7 @@
       </c>
       <c r="AP90" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9*无效</t>
         </is>
       </c>
       <c r="AQ90" s="3" t="inlineStr">
@@ -21071,12 +21071,12 @@
       </c>
       <c r="AR90" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS90" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT90" s="3" t="inlineStr">
